--- a/artfynd/A 42207-2025 artfynd.xlsx
+++ b/artfynd/A 42207-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -973,6 +973,5179 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128650928</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91418</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>693840</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7105970</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128650950</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>693756</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7106020</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128650943</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>693740</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7105800</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128650967</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91471</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>693863</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7105785</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128650968</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91471</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>693709</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7105898</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128650973</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>693705</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7105905</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128650976</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80223</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>693932</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7105871</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128650969</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>694049</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7105886</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128650942</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91453</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>693916</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7105885</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128650978</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80223</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>693730</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7105788</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128650924</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91418</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>694066</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7105738</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128650952</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78841</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>693726</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7105914</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128650954</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>694011</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7105822</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128650957</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>693730</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7105788</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128650938</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79702</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>693762</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7105932</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128650944</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>693908</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7105939</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128650936</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91418</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>693858</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7105746</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128650961</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58055</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>693853</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7105847</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128650972</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>693833</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7105766</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128650971</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>693927</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7105764</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128650923</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91418</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>694058</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7105815</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128650955</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>693928</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7105870</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128650934</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91418</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>693925</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7105884</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128650941</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91453</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>693857</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7105796</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128650956</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>693795</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7105803</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128650927</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91418</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>693860</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7105922</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128650977</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80223</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>693740</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7105800</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128650958</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80224</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>693730</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7105788</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128650925</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91418</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>693910</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7105807</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128650963</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98572</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>693937</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7105866</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128650947</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>693840</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7105879</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128650932</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91418</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>693916</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7105885</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128650951</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80216</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>693767</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7106020</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128650974</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>693724</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7105913</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128650930</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91418</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>693952</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7105933</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128650939</v>
+      </c>
+      <c r="B40" t="n">
+        <v>96919</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1841</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedflikmossa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lophozia guttulata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>693750</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7105955</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128650945</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>693761</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7105937</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128650949</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>693691</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7105892</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128650940</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91453</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>693906</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7105935</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128650975</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>693749</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7106010</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128650966</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91471</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>693923</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7105875</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128650953</v>
+      </c>
+      <c r="B46" t="n">
+        <v>95804</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>693897</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7105882</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128650937</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79702</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>693728</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7105917</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128650935</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91418</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>693886</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7105775</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128650948</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>693845</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7105927</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128650965</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91467</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>694057</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7105822</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128650926</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91418</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>693830</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7105845</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128650962</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78840</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>693726</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7105914</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128650970</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>694008</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7105788</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128650931</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91418</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>693935</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7105909</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128650929</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91418</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>693871</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7105953</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128650946</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91907</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>693901</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7105932</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128650933</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91418</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>693897</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7105878</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42207-2025 artfynd.xlsx
+++ b/artfynd/A 42207-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128556229</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128564841</v>
       </c>
       <c r="B3" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128559270</v>
       </c>
       <c r="B4" t="n">
-        <v>91417</v>
+        <v>91423</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,32 +975,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128650928</v>
+        <v>128650950</v>
       </c>
       <c r="B5" t="n">
-        <v>91418</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1010,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>693840</v>
+        <v>693756</v>
       </c>
       <c r="R5" t="n">
-        <v>7105970</v>
+        <v>7106020</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,6 +1046,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,32 +1077,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128650950</v>
+        <v>128650928</v>
       </c>
       <c r="B6" t="n">
-        <v>57685</v>
+        <v>91423</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1112,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>693756</v>
+        <v>693840</v>
       </c>
       <c r="R6" t="n">
-        <v>7106020</v>
+        <v>7105970</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,11 +1148,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1174,32 +1174,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128650943</v>
+        <v>128650968</v>
       </c>
       <c r="B7" t="n">
-        <v>80217</v>
+        <v>91476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>693740</v>
+        <v>693709</v>
       </c>
       <c r="R7" t="n">
-        <v>7105800</v>
+        <v>7105898</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,32 +1271,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128650967</v>
+        <v>128650943</v>
       </c>
       <c r="B8" t="n">
-        <v>91471</v>
+        <v>80221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>693863</v>
+        <v>693740</v>
       </c>
       <c r="R8" t="n">
-        <v>7105785</v>
+        <v>7105800</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128650968</v>
+        <v>128650967</v>
       </c>
       <c r="B9" t="n">
-        <v>91471</v>
+        <v>91476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>693709</v>
+        <v>693863</v>
       </c>
       <c r="R9" t="n">
-        <v>7105898</v>
+        <v>7105785</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,27 +1465,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128650973</v>
+        <v>128650976</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>80227</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>693705</v>
+        <v>693932</v>
       </c>
       <c r="R10" t="n">
-        <v>7105905</v>
+        <v>7105871</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,27 +1562,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128650976</v>
+        <v>128650969</v>
       </c>
       <c r="B11" t="n">
-        <v>80223</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>693932</v>
+        <v>694049</v>
       </c>
       <c r="R11" t="n">
-        <v>7105871</v>
+        <v>7105886</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1659,27 +1659,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128650969</v>
+        <v>128650978</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>80227</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>694049</v>
+        <v>693730</v>
       </c>
       <c r="R12" t="n">
-        <v>7105886</v>
+        <v>7105788</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1759,7 +1759,7 @@
         <v>128650942</v>
       </c>
       <c r="B13" t="n">
-        <v>91453</v>
+        <v>91458</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1853,27 +1853,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128650978</v>
+        <v>128650973</v>
       </c>
       <c r="B14" t="n">
-        <v>80223</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1888,10 +1888,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>693730</v>
+        <v>693705</v>
       </c>
       <c r="R14" t="n">
-        <v>7105788</v>
+        <v>7105905</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,45 +1950,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128650924</v>
+        <v>128650954</v>
       </c>
       <c r="B15" t="n">
-        <v>91418</v>
+        <v>80192</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stor-Tällvattnet, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>694066</v>
+        <v>694011</v>
       </c>
       <c r="R15" t="n">
-        <v>7105738</v>
+        <v>7105822</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2029,6 +2032,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2047,32 +2051,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128650952</v>
+        <v>128650924</v>
       </c>
       <c r="B16" t="n">
-        <v>78841</v>
+        <v>91423</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2082,10 +2086,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>693726</v>
+        <v>694066</v>
       </c>
       <c r="R16" t="n">
-        <v>7105914</v>
+        <v>7105738</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2144,10 +2148,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128650954</v>
+        <v>128650957</v>
       </c>
       <c r="B17" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2173,19 +2177,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stor-Tällvattnet, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>694011</v>
+        <v>693730</v>
       </c>
       <c r="R17" t="n">
-        <v>7105822</v>
+        <v>7105788</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2226,7 +2227,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128650957</v>
+        <v>128650952</v>
       </c>
       <c r="B18" t="n">
-        <v>80188</v>
+        <v>78845</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2256,21 +2256,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>693730</v>
+        <v>693726</v>
       </c>
       <c r="R18" t="n">
-        <v>7105788</v>
+        <v>7105914</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
         <v>128650938</v>
       </c>
       <c r="B19" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>128650944</v>
       </c>
       <c r="B20" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2536,32 +2536,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128650936</v>
+        <v>128650972</v>
       </c>
       <c r="B21" t="n">
-        <v>91418</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>693858</v>
+        <v>693833</v>
       </c>
       <c r="R21" t="n">
-        <v>7105746</v>
+        <v>7105766</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2636,7 +2636,7 @@
         <v>128650961</v>
       </c>
       <c r="B22" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2730,32 +2730,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128650972</v>
+        <v>128650936</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>91423</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>693833</v>
+        <v>693858</v>
       </c>
       <c r="R23" t="n">
-        <v>7105766</v>
+        <v>7105746</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2830,7 +2830,7 @@
         <v>128650971</v>
       </c>
       <c r="B24" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>128650923</v>
       </c>
       <c r="B25" t="n">
-        <v>91418</v>
+        <v>91423</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>128650955</v>
       </c>
       <c r="B26" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>128650934</v>
       </c>
       <c r="B27" t="n">
-        <v>91418</v>
+        <v>91423</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>128650941</v>
       </c>
       <c r="B28" t="n">
-        <v>91453</v>
+        <v>91458</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3316,48 +3316,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128650956</v>
+        <v>128650927</v>
       </c>
       <c r="B29" t="n">
-        <v>80188</v>
+        <v>91423</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stor-Tällvattnet, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>693795</v>
+        <v>693860</v>
       </c>
       <c r="R29" t="n">
-        <v>7105803</v>
+        <v>7105922</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3398,7 +3395,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3417,10 +3413,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128650927</v>
+        <v>128650977</v>
       </c>
       <c r="B30" t="n">
-        <v>91418</v>
+        <v>80227</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3428,21 +3424,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3452,10 +3448,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>693860</v>
+        <v>693740</v>
       </c>
       <c r="R30" t="n">
-        <v>7105922</v>
+        <v>7105800</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3514,45 +3510,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128650977</v>
+        <v>128650956</v>
       </c>
       <c r="B31" t="n">
-        <v>80223</v>
+        <v>80192</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stor-Tällvattnet, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>693740</v>
+        <v>693795</v>
       </c>
       <c r="R31" t="n">
-        <v>7105800</v>
+        <v>7105803</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3593,6 +3592,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3614,7 +3614,7 @@
         <v>128650958</v>
       </c>
       <c r="B32" t="n">
-        <v>80224</v>
+        <v>80228</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>128650925</v>
       </c>
       <c r="B33" t="n">
-        <v>91418</v>
+        <v>91423</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3805,32 +3805,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128650963</v>
+        <v>128650947</v>
       </c>
       <c r="B34" t="n">
-        <v>98572</v>
+        <v>57689</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>693937</v>
+        <v>693840</v>
       </c>
       <c r="R34" t="n">
-        <v>7105866</v>
+        <v>7105879</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3876,6 +3876,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3902,32 +3907,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128650947</v>
+        <v>128650932</v>
       </c>
       <c r="B35" t="n">
-        <v>57685</v>
+        <v>91423</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3937,10 +3942,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>693840</v>
+        <v>693916</v>
       </c>
       <c r="R35" t="n">
-        <v>7105879</v>
+        <v>7105885</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3973,11 +3978,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4004,32 +4004,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128650932</v>
+        <v>128650963</v>
       </c>
       <c r="B36" t="n">
-        <v>91418</v>
+        <v>98579</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>693916</v>
+        <v>693937</v>
       </c>
       <c r="R36" t="n">
-        <v>7105885</v>
+        <v>7105866</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4104,7 +4104,7 @@
         <v>128650951</v>
       </c>
       <c r="B37" t="n">
-        <v>80216</v>
+        <v>80220</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4198,32 +4198,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128650974</v>
+        <v>128650930</v>
       </c>
       <c r="B38" t="n">
-        <v>79083</v>
+        <v>91423</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>693724</v>
+        <v>693952</v>
       </c>
       <c r="R38" t="n">
-        <v>7105913</v>
+        <v>7105933</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4295,32 +4295,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128650930</v>
+        <v>128650974</v>
       </c>
       <c r="B39" t="n">
-        <v>91418</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>693952</v>
+        <v>693724</v>
       </c>
       <c r="R39" t="n">
-        <v>7105933</v>
+        <v>7105913</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4392,10 +4392,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128650939</v>
+        <v>128650949</v>
       </c>
       <c r="B40" t="n">
-        <v>96919</v>
+        <v>57689</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4403,21 +4403,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1841</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>693750</v>
+        <v>693691</v>
       </c>
       <c r="R40" t="n">
-        <v>7105955</v>
+        <v>7105892</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4463,6 +4463,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4492,7 +4497,7 @@
         <v>128650945</v>
       </c>
       <c r="B41" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4586,10 +4591,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128650949</v>
+        <v>128650940</v>
       </c>
       <c r="B42" t="n">
-        <v>57685</v>
+        <v>91458</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4597,21 +4602,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4621,10 +4626,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>693691</v>
+        <v>693906</v>
       </c>
       <c r="R42" t="n">
-        <v>7105892</v>
+        <v>7105935</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4657,11 +4662,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4688,10 +4688,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128650940</v>
+        <v>128650939</v>
       </c>
       <c r="B43" t="n">
-        <v>91453</v>
+        <v>96924</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4699,21 +4699,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>1841</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4723,10 +4723,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>693906</v>
+        <v>693750</v>
       </c>
       <c r="R43" t="n">
-        <v>7105935</v>
+        <v>7105955</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4788,7 +4788,7 @@
         <v>128650975</v>
       </c>
       <c r="B44" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>128650966</v>
       </c>
       <c r="B45" t="n">
-        <v>91471</v>
+        <v>91476</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>128650953</v>
       </c>
       <c r="B46" t="n">
-        <v>95804</v>
+        <v>95809</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>128650937</v>
       </c>
       <c r="B47" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>128650935</v>
       </c>
       <c r="B48" t="n">
-        <v>91418</v>
+        <v>91423</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>128650948</v>
       </c>
       <c r="B49" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>128650965</v>
       </c>
       <c r="B50" t="n">
-        <v>91467</v>
+        <v>91472</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>128650926</v>
       </c>
       <c r="B51" t="n">
-        <v>91418</v>
+        <v>91423</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>128650962</v>
       </c>
       <c r="B52" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>128650970</v>
       </c>
       <c r="B53" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>128650931</v>
       </c>
       <c r="B54" t="n">
-        <v>91418</v>
+        <v>91423</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5857,10 +5857,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128650929</v>
+        <v>128650933</v>
       </c>
       <c r="B55" t="n">
-        <v>91418</v>
+        <v>91423</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5892,10 +5892,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>693871</v>
+        <v>693897</v>
       </c>
       <c r="R55" t="n">
-        <v>7105953</v>
+        <v>7105878</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5957,7 +5957,7 @@
         <v>128650946</v>
       </c>
       <c r="B56" t="n">
-        <v>91907</v>
+        <v>91912</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6051,10 +6051,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128650933</v>
+        <v>128650929</v>
       </c>
       <c r="B57" t="n">
-        <v>91418</v>
+        <v>91423</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6086,10 +6086,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>693897</v>
+        <v>693871</v>
       </c>
       <c r="R57" t="n">
-        <v>7105878</v>
+        <v>7105953</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6145,6 +6145,107 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128675815</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91740</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>73</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Veckticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Fomitopsis pulvinascens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Stor-Tällvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>694032</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7105769</v>
+      </c>
+      <c r="S58" t="n">
+        <v>50</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42207-2025 artfynd.xlsx
+++ b/artfynd/A 42207-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128564841</v>
       </c>
       <c r="B3" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128559270</v>
       </c>
       <c r="B4" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128650928</v>
       </c>
       <c r="B6" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128650968</v>
       </c>
       <c r="B7" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>128650967</v>
       </c>
       <c r="B9" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>128650942</v>
       </c>
       <c r="B13" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>128650924</v>
       </c>
       <c r="B16" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>128650936</v>
       </c>
       <c r="B23" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>128650923</v>
       </c>
       <c r="B25" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>128650934</v>
       </c>
       <c r="B27" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>128650941</v>
       </c>
       <c r="B28" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>128650927</v>
       </c>
       <c r="B29" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>128650925</v>
       </c>
       <c r="B33" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>128650932</v>
       </c>
       <c r="B35" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128650963</v>
       </c>
       <c r="B36" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>128650930</v>
       </c>
       <c r="B38" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>128650940</v>
       </c>
       <c r="B42" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>128650939</v>
       </c>
       <c r="B43" t="n">
-        <v>96924</v>
+        <v>96930</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>128650966</v>
       </c>
       <c r="B45" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>128650953</v>
       </c>
       <c r="B46" t="n">
-        <v>95809</v>
+        <v>95815</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>128650935</v>
       </c>
       <c r="B48" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>128650965</v>
       </c>
       <c r="B50" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>128650926</v>
       </c>
       <c r="B51" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>128650931</v>
       </c>
       <c r="B54" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>128650933</v>
       </c>
       <c r="B55" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>128650946</v>
       </c>
       <c r="B56" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>128650929</v>
       </c>
       <c r="B57" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>128675815</v>
       </c>
       <c r="B58" t="n">
-        <v>91740</v>
+        <v>91746</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 42207-2025 artfynd.xlsx
+++ b/artfynd/A 42207-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128556229</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128564841</v>
       </c>
       <c r="B3" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128559270</v>
       </c>
       <c r="B4" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128650928</v>
       </c>
       <c r="B6" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128650968</v>
       </c>
       <c r="B7" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128650943</v>
       </c>
       <c r="B8" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>128650967</v>
       </c>
       <c r="B9" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>128650976</v>
       </c>
       <c r="B10" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>128650969</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>128650978</v>
       </c>
       <c r="B12" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>128650942</v>
       </c>
       <c r="B13" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>128650973</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>128650954</v>
       </c>
       <c r="B15" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>128650924</v>
       </c>
       <c r="B16" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>128650957</v>
       </c>
       <c r="B17" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>128650952</v>
       </c>
       <c r="B18" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>128650938</v>
       </c>
       <c r="B19" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>128650972</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>128650936</v>
       </c>
       <c r="B23" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>128650971</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>128650923</v>
       </c>
       <c r="B25" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>128650955</v>
       </c>
       <c r="B26" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>128650934</v>
       </c>
       <c r="B27" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>128650941</v>
       </c>
       <c r="B28" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>128650927</v>
       </c>
       <c r="B29" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>128650977</v>
       </c>
       <c r="B30" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>128650956</v>
       </c>
       <c r="B31" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>128650958</v>
       </c>
       <c r="B32" t="n">
-        <v>80228</v>
+        <v>80230</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>128650925</v>
       </c>
       <c r="B33" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>128650932</v>
       </c>
       <c r="B35" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128650963</v>
       </c>
       <c r="B36" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>128650951</v>
       </c>
       <c r="B37" t="n">
-        <v>80220</v>
+        <v>80222</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>128650930</v>
       </c>
       <c r="B38" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>128650974</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>128650940</v>
       </c>
       <c r="B42" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>128650939</v>
       </c>
       <c r="B43" t="n">
-        <v>96930</v>
+        <v>96932</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>128650975</v>
       </c>
       <c r="B44" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>128650966</v>
       </c>
       <c r="B45" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>128650953</v>
       </c>
       <c r="B46" t="n">
-        <v>95815</v>
+        <v>95817</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>128650937</v>
       </c>
       <c r="B47" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>128650935</v>
       </c>
       <c r="B48" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>128650965</v>
       </c>
       <c r="B50" t="n">
-        <v>91478</v>
+        <v>91480</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>128650926</v>
       </c>
       <c r="B51" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>128650962</v>
       </c>
       <c r="B52" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>128650970</v>
       </c>
       <c r="B53" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>128650931</v>
       </c>
       <c r="B54" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>128650933</v>
       </c>
       <c r="B55" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>128650946</v>
       </c>
       <c r="B56" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>128650929</v>
       </c>
       <c r="B57" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>128675815</v>
       </c>
       <c r="B58" t="n">
-        <v>91746</v>
+        <v>91748</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 42207-2025 artfynd.xlsx
+++ b/artfynd/A 42207-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128564841</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128650963</v>
       </c>
       <c r="B36" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 42207-2025 artfynd.xlsx
+++ b/artfynd/A 42207-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128564841</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128559270</v>
       </c>
       <c r="B4" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128650928</v>
       </c>
       <c r="B6" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128650968</v>
       </c>
       <c r="B7" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>128650967</v>
       </c>
       <c r="B9" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>128650942</v>
       </c>
       <c r="B13" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>128650924</v>
       </c>
       <c r="B16" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>128650936</v>
       </c>
       <c r="B23" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>128650923</v>
       </c>
       <c r="B25" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>128650934</v>
       </c>
       <c r="B27" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>128650941</v>
       </c>
       <c r="B28" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>128650927</v>
       </c>
       <c r="B29" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>128650925</v>
       </c>
       <c r="B33" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>128650932</v>
       </c>
       <c r="B35" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128650963</v>
       </c>
       <c r="B36" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>128650930</v>
       </c>
       <c r="B38" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>128650940</v>
       </c>
       <c r="B42" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>128650939</v>
       </c>
       <c r="B43" t="n">
-        <v>96932</v>
+        <v>96933</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>128650966</v>
       </c>
       <c r="B45" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>128650953</v>
       </c>
       <c r="B46" t="n">
-        <v>95817</v>
+        <v>95818</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>128650935</v>
       </c>
       <c r="B48" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>128650965</v>
       </c>
       <c r="B50" t="n">
-        <v>91480</v>
+        <v>91481</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>128650926</v>
       </c>
       <c r="B51" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>128650931</v>
       </c>
       <c r="B54" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>128650933</v>
       </c>
       <c r="B55" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>128650946</v>
       </c>
       <c r="B56" t="n">
-        <v>91920</v>
+        <v>91921</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>128650929</v>
       </c>
       <c r="B57" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>128675815</v>
       </c>
       <c r="B58" t="n">
-        <v>91748</v>
+        <v>91749</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 42207-2025 artfynd.xlsx
+++ b/artfynd/A 42207-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128556229</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128564841</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128559270</v>
       </c>
       <c r="B4" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>128650950</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128650928</v>
       </c>
       <c r="B6" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128650968</v>
       </c>
       <c r="B7" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128650943</v>
       </c>
       <c r="B8" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>128650967</v>
       </c>
       <c r="B9" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>128650976</v>
       </c>
       <c r="B10" t="n">
-        <v>80229</v>
+        <v>80256</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>128650969</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>128650978</v>
       </c>
       <c r="B12" t="n">
-        <v>80229</v>
+        <v>80256</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>128650942</v>
       </c>
       <c r="B13" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>128650973</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>128650954</v>
       </c>
       <c r="B15" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>128650924</v>
       </c>
       <c r="B16" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>128650957</v>
       </c>
       <c r="B17" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>128650952</v>
       </c>
       <c r="B18" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>128650938</v>
       </c>
       <c r="B19" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>128650944</v>
       </c>
       <c r="B20" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>128650972</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>128650961</v>
       </c>
       <c r="B22" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>128650936</v>
       </c>
       <c r="B23" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>128650971</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>128650923</v>
       </c>
       <c r="B25" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>128650955</v>
       </c>
       <c r="B26" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>128650934</v>
       </c>
       <c r="B27" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>128650941</v>
       </c>
       <c r="B28" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>128650927</v>
       </c>
       <c r="B29" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>128650977</v>
       </c>
       <c r="B30" t="n">
-        <v>80229</v>
+        <v>80256</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>128650956</v>
       </c>
       <c r="B31" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>128650958</v>
       </c>
       <c r="B32" t="n">
-        <v>80230</v>
+        <v>80257</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>128650925</v>
       </c>
       <c r="B33" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>128650947</v>
       </c>
       <c r="B34" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>128650932</v>
       </c>
       <c r="B35" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128650963</v>
       </c>
       <c r="B36" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>128650951</v>
       </c>
       <c r="B37" t="n">
-        <v>80222</v>
+        <v>80249</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>128650930</v>
       </c>
       <c r="B38" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>128650974</v>
       </c>
       <c r="B39" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>128650949</v>
       </c>
       <c r="B40" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>128650945</v>
       </c>
       <c r="B41" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>128650940</v>
       </c>
       <c r="B42" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>128650939</v>
       </c>
       <c r="B43" t="n">
-        <v>96933</v>
+        <v>96960</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>128650975</v>
       </c>
       <c r="B44" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>128650966</v>
       </c>
       <c r="B45" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>128650953</v>
       </c>
       <c r="B46" t="n">
-        <v>95818</v>
+        <v>95845</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>128650937</v>
       </c>
       <c r="B47" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>128650935</v>
       </c>
       <c r="B48" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>128650948</v>
       </c>
       <c r="B49" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>128650965</v>
       </c>
       <c r="B50" t="n">
-        <v>91481</v>
+        <v>91508</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>128650926</v>
       </c>
       <c r="B51" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>128650962</v>
       </c>
       <c r="B52" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>128650970</v>
       </c>
       <c r="B53" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>128650931</v>
       </c>
       <c r="B54" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>128650933</v>
       </c>
       <c r="B55" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>128650946</v>
       </c>
       <c r="B56" t="n">
-        <v>91921</v>
+        <v>91948</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>128650929</v>
       </c>
       <c r="B57" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>128675815</v>
       </c>
       <c r="B58" t="n">
-        <v>91749</v>
+        <v>91776</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 42207-2025 artfynd.xlsx
+++ b/artfynd/A 42207-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128556229</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128564841</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128559270</v>
       </c>
       <c r="B4" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128650928</v>
       </c>
       <c r="B6" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128650968</v>
       </c>
       <c r="B7" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128650943</v>
       </c>
       <c r="B8" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>128650967</v>
       </c>
       <c r="B9" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>128650976</v>
       </c>
       <c r="B10" t="n">
-        <v>80256</v>
+        <v>80260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>128650969</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>128650978</v>
       </c>
       <c r="B12" t="n">
-        <v>80256</v>
+        <v>80260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>128650942</v>
       </c>
       <c r="B13" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>128650973</v>
       </c>
       <c r="B14" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>128650954</v>
       </c>
       <c r="B15" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>128650924</v>
       </c>
       <c r="B16" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>128650957</v>
       </c>
       <c r="B17" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>128650952</v>
       </c>
       <c r="B18" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>128650938</v>
       </c>
       <c r="B19" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>128650972</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>128650936</v>
       </c>
       <c r="B23" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>128650971</v>
       </c>
       <c r="B24" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>128650923</v>
       </c>
       <c r="B25" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>128650955</v>
       </c>
       <c r="B26" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>128650934</v>
       </c>
       <c r="B27" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>128650941</v>
       </c>
       <c r="B28" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>128650927</v>
       </c>
       <c r="B29" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>128650977</v>
       </c>
       <c r="B30" t="n">
-        <v>80256</v>
+        <v>80260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>128650956</v>
       </c>
       <c r="B31" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>128650958</v>
       </c>
       <c r="B32" t="n">
-        <v>80257</v>
+        <v>80261</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>128650925</v>
       </c>
       <c r="B33" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>128650932</v>
       </c>
       <c r="B35" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128650963</v>
       </c>
       <c r="B36" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>128650951</v>
       </c>
       <c r="B37" t="n">
-        <v>80249</v>
+        <v>80253</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>128650930</v>
       </c>
       <c r="B38" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>128650974</v>
       </c>
       <c r="B39" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>128650940</v>
       </c>
       <c r="B42" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>128650939</v>
       </c>
       <c r="B43" t="n">
-        <v>96960</v>
+        <v>96966</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>128650975</v>
       </c>
       <c r="B44" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>128650966</v>
       </c>
       <c r="B45" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>128650953</v>
       </c>
       <c r="B46" t="n">
-        <v>95845</v>
+        <v>95851</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>128650937</v>
       </c>
       <c r="B47" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>128650935</v>
       </c>
       <c r="B48" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>128650965</v>
       </c>
       <c r="B50" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>128650926</v>
       </c>
       <c r="B51" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>128650962</v>
       </c>
       <c r="B52" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>128650970</v>
       </c>
       <c r="B53" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>128650931</v>
       </c>
       <c r="B54" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>128650933</v>
       </c>
       <c r="B55" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>128650946</v>
       </c>
       <c r="B56" t="n">
-        <v>91948</v>
+        <v>91953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>128650929</v>
       </c>
       <c r="B57" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>128675815</v>
       </c>
       <c r="B58" t="n">
-        <v>91776</v>
+        <v>91781</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 42207-2025 artfynd.xlsx
+++ b/artfynd/A 42207-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128564841</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128559270</v>
       </c>
       <c r="B4" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128650928</v>
       </c>
       <c r="B6" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128650968</v>
       </c>
       <c r="B7" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>128650967</v>
       </c>
       <c r="B9" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>128650942</v>
       </c>
       <c r="B13" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>128650924</v>
       </c>
       <c r="B16" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>128650936</v>
       </c>
       <c r="B23" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>128650923</v>
       </c>
       <c r="B25" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>128650934</v>
       </c>
       <c r="B27" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>128650941</v>
       </c>
       <c r="B28" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>128650927</v>
       </c>
       <c r="B29" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>128650925</v>
       </c>
       <c r="B33" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>128650932</v>
       </c>
       <c r="B35" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128650963</v>
       </c>
       <c r="B36" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>128650930</v>
       </c>
       <c r="B38" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>128650940</v>
       </c>
       <c r="B42" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>128650939</v>
       </c>
       <c r="B43" t="n">
-        <v>96966</v>
+        <v>96973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>128650966</v>
       </c>
       <c r="B45" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>128650953</v>
       </c>
       <c r="B46" t="n">
-        <v>95851</v>
+        <v>95858</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>128650935</v>
       </c>
       <c r="B48" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>128650965</v>
       </c>
       <c r="B50" t="n">
-        <v>91513</v>
+        <v>91518</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>128650926</v>
       </c>
       <c r="B51" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>128650931</v>
       </c>
       <c r="B54" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>128650933</v>
       </c>
       <c r="B55" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>128650946</v>
       </c>
       <c r="B56" t="n">
-        <v>91953</v>
+        <v>91958</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>128650929</v>
       </c>
       <c r="B57" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>128675815</v>
       </c>
       <c r="B58" t="n">
-        <v>91781</v>
+        <v>91786</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 42207-2025 artfynd.xlsx
+++ b/artfynd/A 42207-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128556229</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128564841</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128559270</v>
       </c>
       <c r="B4" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>128650950</v>
       </c>
       <c r="B5" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128650928</v>
       </c>
       <c r="B6" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128650968</v>
       </c>
       <c r="B7" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128650943</v>
       </c>
       <c r="B8" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>128650967</v>
       </c>
       <c r="B9" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>128650976</v>
       </c>
       <c r="B10" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>128650969</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>128650978</v>
       </c>
       <c r="B12" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>128650942</v>
       </c>
       <c r="B13" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>128650973</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>128650954</v>
       </c>
       <c r="B15" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>128650924</v>
       </c>
       <c r="B16" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>128650957</v>
       </c>
       <c r="B17" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>128650952</v>
       </c>
       <c r="B18" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>128650938</v>
       </c>
       <c r="B19" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>128650944</v>
       </c>
       <c r="B20" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>128650972</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>128650961</v>
       </c>
       <c r="B22" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>128650936</v>
       </c>
       <c r="B23" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>128650971</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>128650923</v>
       </c>
       <c r="B25" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>128650955</v>
       </c>
       <c r="B26" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>128650934</v>
       </c>
       <c r="B27" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>128650941</v>
       </c>
       <c r="B28" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>128650927</v>
       </c>
       <c r="B29" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>128650977</v>
       </c>
       <c r="B30" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>128650956</v>
       </c>
       <c r="B31" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>128650958</v>
       </c>
       <c r="B32" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>128650925</v>
       </c>
       <c r="B33" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>128650947</v>
       </c>
       <c r="B34" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>128650932</v>
       </c>
       <c r="B35" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128650963</v>
       </c>
       <c r="B36" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>128650951</v>
       </c>
       <c r="B37" t="n">
-        <v>80253</v>
+        <v>80257</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>128650930</v>
       </c>
       <c r="B38" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>128650974</v>
       </c>
       <c r="B39" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>128650949</v>
       </c>
       <c r="B40" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>128650945</v>
       </c>
       <c r="B41" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>128650940</v>
       </c>
       <c r="B42" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>128650939</v>
       </c>
       <c r="B43" t="n">
-        <v>96973</v>
+        <v>96977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>128650975</v>
       </c>
       <c r="B44" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>128650966</v>
       </c>
       <c r="B45" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>128650953</v>
       </c>
       <c r="B46" t="n">
-        <v>95858</v>
+        <v>95862</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>128650937</v>
       </c>
       <c r="B47" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>128650935</v>
       </c>
       <c r="B48" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>128650948</v>
       </c>
       <c r="B49" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>128650965</v>
       </c>
       <c r="B50" t="n">
-        <v>91518</v>
+        <v>91522</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>128650926</v>
       </c>
       <c r="B51" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>128650962</v>
       </c>
       <c r="B52" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>128650970</v>
       </c>
       <c r="B53" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>128650931</v>
       </c>
       <c r="B54" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>128650933</v>
       </c>
       <c r="B55" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>128650946</v>
       </c>
       <c r="B56" t="n">
-        <v>91958</v>
+        <v>91962</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>128650929</v>
       </c>
       <c r="B57" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>128675815</v>
       </c>
       <c r="B58" t="n">
-        <v>91786</v>
+        <v>91790</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 42207-2025 artfynd.xlsx
+++ b/artfynd/A 42207-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128556229</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128564841</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128559270</v>
       </c>
       <c r="B4" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>128650950</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128650928</v>
       </c>
       <c r="B6" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128650968</v>
       </c>
       <c r="B7" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128650943</v>
       </c>
       <c r="B8" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>128650967</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>128650976</v>
       </c>
       <c r="B10" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>128650969</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>128650978</v>
       </c>
       <c r="B12" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>128650942</v>
       </c>
       <c r="B13" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>128650973</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>128650954</v>
       </c>
       <c r="B15" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>128650924</v>
       </c>
       <c r="B16" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>128650957</v>
       </c>
       <c r="B17" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>128650952</v>
       </c>
       <c r="B18" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>128650938</v>
       </c>
       <c r="B19" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>128650944</v>
       </c>
       <c r="B20" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>128650972</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>128650961</v>
       </c>
       <c r="B22" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>128650936</v>
       </c>
       <c r="B23" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>128650971</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>128650923</v>
       </c>
       <c r="B25" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>128650955</v>
       </c>
       <c r="B26" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>128650934</v>
       </c>
       <c r="B27" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>128650941</v>
       </c>
       <c r="B28" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>128650927</v>
       </c>
       <c r="B29" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>128650977</v>
       </c>
       <c r="B30" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>128650956</v>
       </c>
       <c r="B31" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>128650958</v>
       </c>
       <c r="B32" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>128650925</v>
       </c>
       <c r="B33" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>128650947</v>
       </c>
       <c r="B34" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>128650932</v>
       </c>
       <c r="B35" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128650963</v>
       </c>
       <c r="B36" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>128650951</v>
       </c>
       <c r="B37" t="n">
-        <v>80257</v>
+        <v>80162</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>128650930</v>
       </c>
       <c r="B38" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>128650974</v>
       </c>
       <c r="B39" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>128650949</v>
       </c>
       <c r="B40" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>128650945</v>
       </c>
       <c r="B41" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>128650940</v>
       </c>
       <c r="B42" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>128650939</v>
       </c>
       <c r="B43" t="n">
-        <v>96977</v>
+        <v>96984</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>128650975</v>
       </c>
       <c r="B44" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>128650966</v>
       </c>
       <c r="B45" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>128650953</v>
       </c>
       <c r="B46" t="n">
-        <v>95862</v>
+        <v>95869</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>128650937</v>
       </c>
       <c r="B47" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>128650935</v>
       </c>
       <c r="B48" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>128650948</v>
       </c>
       <c r="B49" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>128650965</v>
       </c>
       <c r="B50" t="n">
-        <v>91522</v>
+        <v>91527</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>128650926</v>
       </c>
       <c r="B51" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>128650962</v>
       </c>
       <c r="B52" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>128650970</v>
       </c>
       <c r="B53" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>128650931</v>
       </c>
       <c r="B54" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>128650933</v>
       </c>
       <c r="B55" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>128650946</v>
       </c>
       <c r="B56" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>128650929</v>
       </c>
       <c r="B57" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>128675815</v>
       </c>
       <c r="B58" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 42207-2025 artfynd.xlsx
+++ b/artfynd/A 42207-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128556229</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128564841</v>
       </c>
       <c r="B3" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128559270</v>
       </c>
       <c r="B4" t="n">
-        <v>91480</v>
+        <v>91485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128650928</v>
       </c>
       <c r="B6" t="n">
-        <v>91480</v>
+        <v>91485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128650968</v>
       </c>
       <c r="B7" t="n">
-        <v>91533</v>
+        <v>91538</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128650943</v>
       </c>
       <c r="B8" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>128650967</v>
       </c>
       <c r="B9" t="n">
-        <v>91533</v>
+        <v>91538</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>128650976</v>
       </c>
       <c r="B10" t="n">
-        <v>80169</v>
+        <v>80174</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>128650969</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>128650978</v>
       </c>
       <c r="B12" t="n">
-        <v>80169</v>
+        <v>80174</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>128650942</v>
       </c>
       <c r="B13" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>128650973</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>128650954</v>
       </c>
       <c r="B15" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>128650924</v>
       </c>
       <c r="B16" t="n">
-        <v>91480</v>
+        <v>91485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>128650957</v>
       </c>
       <c r="B17" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>128650952</v>
       </c>
       <c r="B18" t="n">
-        <v>78787</v>
+        <v>78792</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>128650938</v>
       </c>
       <c r="B19" t="n">
-        <v>79648</v>
+        <v>79653</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>128650972</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>128650936</v>
       </c>
       <c r="B23" t="n">
-        <v>91480</v>
+        <v>91485</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>128650971</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>128650923</v>
       </c>
       <c r="B25" t="n">
-        <v>91480</v>
+        <v>91485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>128650955</v>
       </c>
       <c r="B26" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>128650934</v>
       </c>
       <c r="B27" t="n">
-        <v>91480</v>
+        <v>91485</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>128650941</v>
       </c>
       <c r="B28" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>128650927</v>
       </c>
       <c r="B29" t="n">
-        <v>91480</v>
+        <v>91485</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>128650977</v>
       </c>
       <c r="B30" t="n">
-        <v>80169</v>
+        <v>80174</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>128650956</v>
       </c>
       <c r="B31" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>128650958</v>
       </c>
       <c r="B32" t="n">
-        <v>80170</v>
+        <v>80175</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>128650925</v>
       </c>
       <c r="B33" t="n">
-        <v>91480</v>
+        <v>91485</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>128650932</v>
       </c>
       <c r="B35" t="n">
-        <v>91480</v>
+        <v>91485</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128650963</v>
       </c>
       <c r="B36" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>128650951</v>
       </c>
       <c r="B37" t="n">
-        <v>80162</v>
+        <v>80167</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>128650930</v>
       </c>
       <c r="B38" t="n">
-        <v>91480</v>
+        <v>91485</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>128650974</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>128650940</v>
       </c>
       <c r="B42" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>128650939</v>
       </c>
       <c r="B43" t="n">
-        <v>96987</v>
+        <v>96992</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>128650975</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>128650966</v>
       </c>
       <c r="B45" t="n">
-        <v>91533</v>
+        <v>91538</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>128650953</v>
       </c>
       <c r="B46" t="n">
-        <v>95872</v>
+        <v>95877</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>128650937</v>
       </c>
       <c r="B47" t="n">
-        <v>79648</v>
+        <v>79653</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>128650935</v>
       </c>
       <c r="B48" t="n">
-        <v>91480</v>
+        <v>91485</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>128650965</v>
       </c>
       <c r="B50" t="n">
-        <v>91529</v>
+        <v>91534</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>128650926</v>
       </c>
       <c r="B51" t="n">
-        <v>91480</v>
+        <v>91485</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>128650962</v>
       </c>
       <c r="B52" t="n">
-        <v>78786</v>
+        <v>78791</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>128650970</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>128650931</v>
       </c>
       <c r="B54" t="n">
-        <v>91480</v>
+        <v>91485</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>128650933</v>
       </c>
       <c r="B55" t="n">
-        <v>91480</v>
+        <v>91485</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>128650946</v>
       </c>
       <c r="B56" t="n">
-        <v>91970</v>
+        <v>91975</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>128650929</v>
       </c>
       <c r="B57" t="n">
-        <v>91480</v>
+        <v>91485</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>128675815</v>
       </c>
       <c r="B58" t="n">
-        <v>91797</v>
+        <v>91802</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 42207-2025 artfynd.xlsx
+++ b/artfynd/A 42207-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128556229</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128564841</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128559270</v>
       </c>
       <c r="B4" t="n">
-        <v>91485</v>
+        <v>91491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128650928</v>
       </c>
       <c r="B6" t="n">
-        <v>91485</v>
+        <v>91491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128650968</v>
       </c>
       <c r="B7" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128650943</v>
       </c>
       <c r="B8" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>128650967</v>
       </c>
       <c r="B9" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>128650976</v>
       </c>
       <c r="B10" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>128650969</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>128650978</v>
       </c>
       <c r="B12" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>128650942</v>
       </c>
       <c r="B13" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>128650973</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>128650954</v>
       </c>
       <c r="B15" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>128650924</v>
       </c>
       <c r="B16" t="n">
-        <v>91485</v>
+        <v>91491</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>128650957</v>
       </c>
       <c r="B17" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>128650952</v>
       </c>
       <c r="B18" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>128650938</v>
       </c>
       <c r="B19" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>128650972</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>128650936</v>
       </c>
       <c r="B23" t="n">
-        <v>91485</v>
+        <v>91491</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>128650971</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>128650923</v>
       </c>
       <c r="B25" t="n">
-        <v>91485</v>
+        <v>91491</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>128650955</v>
       </c>
       <c r="B26" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>128650934</v>
       </c>
       <c r="B27" t="n">
-        <v>91485</v>
+        <v>91491</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>128650941</v>
       </c>
       <c r="B28" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>128650927</v>
       </c>
       <c r="B29" t="n">
-        <v>91485</v>
+        <v>91491</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>128650977</v>
       </c>
       <c r="B30" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>128650956</v>
       </c>
       <c r="B31" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>128650958</v>
       </c>
       <c r="B32" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>128650925</v>
       </c>
       <c r="B33" t="n">
-        <v>91485</v>
+        <v>91491</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>128650932</v>
       </c>
       <c r="B35" t="n">
-        <v>91485</v>
+        <v>91491</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128650963</v>
       </c>
       <c r="B36" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>128650951</v>
       </c>
       <c r="B37" t="n">
-        <v>80167</v>
+        <v>80168</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>128650930</v>
       </c>
       <c r="B38" t="n">
-        <v>91485</v>
+        <v>91491</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>128650974</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>128650940</v>
       </c>
       <c r="B42" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>128650939</v>
       </c>
       <c r="B43" t="n">
-        <v>96992</v>
+        <v>97000</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>128650975</v>
       </c>
       <c r="B44" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>128650966</v>
       </c>
       <c r="B45" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>128650953</v>
       </c>
       <c r="B46" t="n">
-        <v>95877</v>
+        <v>95885</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>128650937</v>
       </c>
       <c r="B47" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>128650935</v>
       </c>
       <c r="B48" t="n">
-        <v>91485</v>
+        <v>91491</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>128650965</v>
       </c>
       <c r="B50" t="n">
-        <v>91534</v>
+        <v>91540</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>128650926</v>
       </c>
       <c r="B51" t="n">
-        <v>91485</v>
+        <v>91491</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>128650962</v>
       </c>
       <c r="B52" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>128650970</v>
       </c>
       <c r="B53" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>128650931</v>
       </c>
       <c r="B54" t="n">
-        <v>91485</v>
+        <v>91491</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>128650933</v>
       </c>
       <c r="B55" t="n">
-        <v>91485</v>
+        <v>91491</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>128650946</v>
       </c>
       <c r="B56" t="n">
-        <v>91975</v>
+        <v>91981</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>128650929</v>
       </c>
       <c r="B57" t="n">
-        <v>91485</v>
+        <v>91491</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>128675815</v>
       </c>
       <c r="B58" t="n">
-        <v>91802</v>
+        <v>91808</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 42207-2025 artfynd.xlsx
+++ b/artfynd/A 42207-2025 artfynd.xlsx
@@ -978,7 +978,7 @@
         <v>128650950</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128650928</v>
       </c>
       <c r="B6" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128650968</v>
       </c>
       <c r="B7" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128650943</v>
       </c>
       <c r="B8" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>128650967</v>
       </c>
       <c r="B9" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>128650976</v>
       </c>
       <c r="B10" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>128650969</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>128650978</v>
       </c>
       <c r="B12" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>128650942</v>
       </c>
       <c r="B13" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>128650973</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>128650954</v>
       </c>
       <c r="B15" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>128650924</v>
       </c>
       <c r="B16" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>128650957</v>
       </c>
       <c r="B17" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>128650952</v>
       </c>
       <c r="B18" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>128650938</v>
       </c>
       <c r="B19" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>128650944</v>
       </c>
       <c r="B20" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>128650972</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>128650961</v>
       </c>
       <c r="B22" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>128650936</v>
       </c>
       <c r="B23" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>128650971</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>128650923</v>
       </c>
       <c r="B25" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>128650955</v>
       </c>
       <c r="B26" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>128650934</v>
       </c>
       <c r="B27" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>128650941</v>
       </c>
       <c r="B28" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>128650927</v>
       </c>
       <c r="B29" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>128650977</v>
       </c>
       <c r="B30" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>128650956</v>
       </c>
       <c r="B31" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>128650958</v>
       </c>
       <c r="B32" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>128650925</v>
       </c>
       <c r="B33" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>128650947</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>128650932</v>
       </c>
       <c r="B35" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128650963</v>
       </c>
       <c r="B36" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>128650951</v>
       </c>
       <c r="B37" t="n">
-        <v>80168</v>
+        <v>80172</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>128650930</v>
       </c>
       <c r="B38" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>128650974</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>128650949</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>128650945</v>
       </c>
       <c r="B41" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>128650940</v>
       </c>
       <c r="B42" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>128650939</v>
       </c>
       <c r="B43" t="n">
-        <v>97000</v>
+        <v>97010</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>128650975</v>
       </c>
       <c r="B44" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>128650966</v>
       </c>
       <c r="B45" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>128650953</v>
       </c>
       <c r="B46" t="n">
-        <v>95885</v>
+        <v>95895</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>128650937</v>
       </c>
       <c r="B47" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>128650935</v>
       </c>
       <c r="B48" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>128650948</v>
       </c>
       <c r="B49" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>128650965</v>
       </c>
       <c r="B50" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>128650926</v>
       </c>
       <c r="B51" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>128650962</v>
       </c>
       <c r="B52" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>128650970</v>
       </c>
       <c r="B53" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>128650931</v>
       </c>
       <c r="B54" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>128650933</v>
       </c>
       <c r="B55" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>128650946</v>
       </c>
       <c r="B56" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>128650929</v>
       </c>
       <c r="B57" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>128675815</v>
       </c>
       <c r="B58" t="n">
-        <v>91808</v>
+        <v>91815</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
